--- a/DH production mix/four_category.xlsx
+++ b/DH production mix/four_category.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\yangzhe\myprojects\EIA_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\yangzhe\myprojects\EIA_2026\DH production mix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECA8841-3CDA-4984-B2B2-2CB323B05F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D677DAAC-ED65-40AD-BC59-73E73178C43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="24" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>Oppsummering (MWh)</t>
   </si>
@@ -271,6 +271,18 @@
   </si>
   <si>
     <t>2025-12</t>
+  </si>
+  <si>
+    <t>Waste heat</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>Fossil fuel</t>
   </si>
 </sst>
 </file>
@@ -825,7 +837,11 @@
   <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -833,16 +849,16 @@
         <v>30</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1165,7 +1181,7 @@
         <v>16</v>
       </c>
       <c r="E20">
-        <v>-15</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
